--- a/数据表/Datas/EntityConfig_实体配置.xlsx
+++ b/数据表/Datas/EntityConfig_实体配置.xlsx
@@ -27,23 +27,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>assetName</t>
   </si>
   <si>
+    <t>prefabPath</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -56,50 +53,128 @@
     <t>##</t>
   </si>
   <si>
+    <t>资源名称</t>
+  </si>
+  <si>
+    <r>
+      <t>资源路径（相较于</t>
+    </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Assets/GameMain/Entities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color rgb="FF9C0006"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>实体编号</t>
+      <t>）</t>
     </r>
   </si>
   <si>
+    <r>
+      <t>##</t>
+    </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF9C0006"/>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
-      <t>资源名称</t>
+      <t>资源点</t>
     </r>
   </si>
   <si>
-    <t>PlayerShip</t>
-  </si>
-  <si>
-    <t>EnemyShip</t>
-  </si>
-  <si>
-    <t>PlayerEngine</t>
-  </si>
-  <si>
-    <t>EnemyEngine</t>
-  </si>
-  <si>
-    <t>DefaultWeapon</t>
-  </si>
-  <si>
-    <t>DefaultArmor</t>
-  </si>
-  <si>
-    <t>PlayerBolt</t>
-  </si>
-  <si>
-    <t>EnemyBolt</t>
+    <t>ResourcePoint</t>
+  </si>
+  <si>
+    <t>ResourcePoint1</t>
+  </si>
+  <si>
+    <t>ResourcePoint2</t>
+  </si>
+  <si>
+    <t>ResourcePoint3</t>
+  </si>
+  <si>
+    <t>ResourcePoint4</t>
+  </si>
+  <si>
+    <t>ResourcePoint5</t>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyUnit</t>
+  </si>
+  <si>
+    <t>EnemyPartyLowThreat</t>
+  </si>
+  <si>
+    <t>EnemyPartyMiddleThreat</t>
+  </si>
+  <si>
+    <t>EnemyPartyHighThreat</t>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家</t>
+    </r>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Character1</t>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图</t>
+    </r>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>EvacuatePoint</t>
   </si>
 </sst>
 </file>
@@ -112,43 +187,49 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <name val="Andale Mono"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF006100"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF1F4E78"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF595959"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
@@ -305,13 +386,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,18 +444,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -712,82 +781,88 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -796,10 +871,10 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -808,10 +883,10 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -820,10 +895,10 @@
     <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -832,10 +907,10 @@
     <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -844,63 +919,52 @@
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1373,141 +1437,216 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="1" max="1" width="13.3529411764706" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5735294117647" style="2" customWidth="1"/>
+    <col min="3" max="3" width="45.8308823529412" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" customHeight="1" spans="1:4">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:4">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" customHeight="1" spans="1:4">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12">
-        <v>10001</v>
-      </c>
-      <c r="C6" s="13" t="s">
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" customHeight="1" spans="1:4">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12">
-        <v>20000</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="str">
+        <f t="shared" ref="C7:C11" si="0">B$6&amp;"/"&amp;B7&amp;".prefab"</f>
+        <v>ResourcePoint/ResourcePoint1.prefab</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" customHeight="1" spans="1:4">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12">
-        <v>20001</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint2.prefab</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" customHeight="1" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12">
-        <v>30000</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint3.prefab</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12">
-        <v>40000</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint4.prefab</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:4">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12">
-        <v>50000</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>ResourcePoint/ResourcePoint5.prefab</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:4">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12">
-        <v>50001</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="B14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="11" t="str">
+        <f t="shared" ref="C14:C16" si="1">B$13&amp;"/"&amp;B14&amp;".prefab"</f>
+        <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>EnemyUnit/EnemyPartyMiddleThreat.prefab</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>EnemyUnit/EnemyPartyHighThreat.prefab</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="11"/>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="B19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="11" t="str">
+        <f>B$18&amp;"/"&amp;B19&amp;".prefab"</f>
+        <v>Character/Character1.prefab</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21" customHeight="1" spans="1:3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="11" t="str">
+        <f>B$22&amp;"/"&amp;B23&amp;".prefab"</f>
+        <v>Map/EvacuatePoint.prefab</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/EntityConfig_实体配置.xlsx
+++ b/数据表/Datas/EntityConfig_实体配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -53,17 +58,31 @@
     <t>##</t>
   </si>
   <si>
-    <t>资源名称</t>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资源名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>资源路径（相较于</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>Assets/GameMain/Entities</t>
@@ -72,7 +91,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -86,7 +105,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>资源点</t>
@@ -118,7 +137,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -144,7 +163,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>玩家</t>
@@ -154,7 +173,10 @@
     <t>Character</t>
   </si>
   <si>
-    <t>Character1</t>
+    <t>CharacterLeader</t>
+  </si>
+  <si>
+    <t>CharacterRetinue</t>
   </si>
   <si>
     <r>
@@ -164,7 +186,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>地图</t>
@@ -175,6 +197,9 @@
   </si>
   <si>
     <t>EvacuatePoint</t>
+  </si>
+  <si>
+    <t>MainCamera</t>
   </si>
 </sst>
 </file>
@@ -195,43 +220,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -387,8 +406,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -784,163 +809,157 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -954,17 +973,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1437,215 +1447,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="13.3529411764706" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5735294117647" style="2" customWidth="1"/>
-    <col min="3" max="3" width="45.8308823529412" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="13.35" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.575" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45.8333333333333" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11" t="str">
+      <c r="C7" s="1" t="str">
         <f t="shared" ref="C7:C11" si="0">B$6&amp;"/"&amp;B7&amp;".prefab"</f>
         <v>ResourcePoint/ResourcePoint1.prefab</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="str">
+      <c r="C8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>ResourcePoint/ResourcePoint2.prefab</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11" t="str">
+      <c r="C9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>ResourcePoint/ResourcePoint3.prefab</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="11" t="str">
+      <c r="C10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>ResourcePoint/ResourcePoint4.prefab</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="11" t="str">
+      <c r="C11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>ResourcePoint/ResourcePoint5.prefab</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="11"/>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="11" t="str">
+      <c r="C14" s="1" t="str">
         <f t="shared" ref="C14:C16" si="1">B$13&amp;"/"&amp;B14&amp;".prefab"</f>
         <v>EnemyUnit/EnemyPartyLowThreat.prefab</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="11" t="str">
+      <c r="C15" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EnemyUnit/EnemyPartyMiddleThreat.prefab</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="11" t="str">
+      <c r="C16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>EnemyUnit/EnemyPartyHighThreat.prefab</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="11"/>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="11" t="str">
+      <c r="C19" s="1" t="str">
         <f>B$18&amp;"/"&amp;B19&amp;".prefab"</f>
-        <v>Character/Character1.prefab</v>
+        <v>Character/CharacterLeader.prefab</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <f>B$18&amp;"/"&amp;B20&amp;".prefab"</f>
+        <v>Character/CharacterRetinue.prefab</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="11"/>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="11" t="str">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="str">
         <f>B$22&amp;"/"&amp;B23&amp;".prefab"</f>
         <v>Map/EvacuatePoint.prefab</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f>B$22&amp;"/"&amp;B24&amp;".prefab"</f>
+        <v>Map/MainCamera.prefab</v>
       </c>
     </row>
   </sheetData>
